--- a/documents/01-需求阶段/需求跟踪矩阵.xlsx
+++ b/documents/01-需求阶段/需求跟踪矩阵.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1StarTracker\documents\01-需求阶段\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58B5B98-7DD4-4C19-B93C-2963A45AA875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B087B7BF-DE36-489F-8135-06B87E38D998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="基本功能" sheetId="1" r:id="rId1"/>
     <sheet name="操作功能" sheetId="2" r:id="rId2"/>
     <sheet name="性能需求（精度）" sheetId="3" r:id="rId3"/>
-    <sheet name="性能需求（光学）" sheetId="4" r:id="rId4"/>
-    <sheet name="性能需求（可靠性）" sheetId="5" r:id="rId5"/>
-    <sheet name="接口需求（电气）" sheetId="6" r:id="rId6"/>
-    <sheet name="接口需求（机械）" sheetId="7" r:id="rId7"/>
-    <sheet name="接口需求（通信）" sheetId="8" r:id="rId8"/>
-    <sheet name="环境需求（温度）" sheetId="9" r:id="rId9"/>
-    <sheet name="环境需求（力学）" sheetId="11" r:id="rId10"/>
-    <sheet name="环境需求（其它）" sheetId="10" r:id="rId11"/>
-    <sheet name="安全与可靠性（电气）" sheetId="12" r:id="rId12"/>
-    <sheet name="安全与可靠性（功能）" sheetId="13" r:id="rId13"/>
-    <sheet name="安全与可靠性（辐射）" sheetId="14" r:id="rId14"/>
+    <sheet name="软件需求" sheetId="17" r:id="rId4"/>
+    <sheet name="性能需求（光学）" sheetId="4" r:id="rId5"/>
+    <sheet name="性能需求（可靠性）" sheetId="5" r:id="rId6"/>
+    <sheet name="接口需求（电气）" sheetId="6" r:id="rId7"/>
+    <sheet name="接口需求（机械）" sheetId="7" r:id="rId8"/>
+    <sheet name="接口需求（通信）" sheetId="8" r:id="rId9"/>
+    <sheet name="环境需求（温度）" sheetId="9" r:id="rId10"/>
+    <sheet name="环境需求（力学）" sheetId="11" r:id="rId11"/>
+    <sheet name="环境需求（其它）" sheetId="10" r:id="rId12"/>
+    <sheet name="安全与可靠性（电气）" sheetId="12" r:id="rId13"/>
+    <sheet name="安全与可靠性（功能）" sheetId="13" r:id="rId14"/>
     <sheet name="维护性需求" sheetId="15" r:id="rId15"/>
     <sheet name="文档要求" sheetId="16" r:id="rId16"/>
   </sheets>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="361">
   <si>
     <t>需求ID</t>
   </si>
@@ -146,11 +146,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>支持UART或USB接口升级
-问题：这里的UAR是什么？固件是硬件吗？它是怎么升级的？尤其当星敏感器被发射到太空后？为什么这里没有软件升级？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>中</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -178,35 +173,13 @@
     <t>URS-PER-005</t>
   </si>
   <si>
-    <t>相对精度（跨视轴）
-视轴是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>≤10 arcsec (RMS)</t>
   </si>
   <si>
-    <t>问题
-1.为什么这里的表头和基本功能和操作功能不一样了？
-2.如何区分这里的内容和测试文档？因为我注意到表格中有一列就是‘测试条件’难道说测试手册中要写的更详细吗？而这里只是给出了最低的底线要求？
-如何区分指标要求和测试条件？比如第一条的跨视轴要求，一个是要求≤10arcsec，另一个又说让视场中≥5颗星？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>常温，视场内≥5颗星</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>噪声等效角
-为什么噪声可以用角度来衡量？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>≤5 arcsec (RMS)
-RMS是什么指标？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>静态测试，积分时间200ms</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -218,11 +191,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>绝对精度（含校准误差）
-和相对精度的区别是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>姿态输出更新率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -294,11 +262,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>不饱和且可探测
-什么意思？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>≤0.1%（全视场）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -396,16 +359,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>过压、反接保护
-什么意思？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从上电到有效输出
-什么是上电，什么是有效输出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> RS422，波特率可配置（默认115200）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -640,11 +593,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工作状态
-这是什么意思？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>URS-ENV-007</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -730,11 +678,6 @@
     <t>URS-SAF-007</t>
   </si>
   <si>
-    <t>看门狗
-这是什么？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>数据完整性</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -743,9 +686,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>硬件看门狗，超时时间1.6秒</t>
-  </si>
-  <si>
     <t>关键数据三重存储，EDAC保护</t>
   </si>
   <si>
@@ -770,15 +710,6 @@
     <t xml:space="preserve"> URS-MNT-006</t>
   </si>
   <si>
-    <t xml:space="preserve"> URS-MNT-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URS-MNT-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URS-MNT-009</t>
-  </si>
-  <si>
     <t>内置自检（BIT）</t>
   </si>
   <si>
@@ -790,11 +721,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>关键信号预留测试点（电源，时钟，复位
-问题：这是什么意思？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>诊断接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -909,6 +835,458 @@
   </si>
   <si>
     <t>交付格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持UART（异步串行通信协议）或USB接口升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试条件（环境准备）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨视轴相对精度（跨视轴）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本设计将所有噪声均视为视场抖动，并根据抖动视场角来衡量噪声（等效角）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>噪声等效角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>≤5 arcsec (RMS均方根)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不饱和且可探测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不饱和指星点不过曝，可探测指对比度足以区分星点和环境</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从上电到有效输出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设计需配备防止过压、反接的保护电路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看门狗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬件定时器，程序卡死时自动重启系统，约定超时时间为1.6秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预留焊接点位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关键信号预留测试点（电源，时钟，复位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝对精度定义为于真实值（外部参考系）的偏差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>视轴是中心光轴，此处定义为cmos中心像素向外的射线，相对精度指：短时间连续几次拍摄得到姿态时，输出一致性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝对精度（含校准误差）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>验收标准/指标</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>测试条件/备注</t>
+  </si>
+  <si>
+    <t>初始化与自检</t>
+  </si>
+  <si>
+    <t>URS-SW-001</t>
+  </si>
+  <si>
+    <t>软件支持上电自动初始化所有硬件模块（探测器、通信接口、存储等）</t>
+  </si>
+  <si>
+    <t>上电后1秒内完成硬件初始化并进入自检阶段</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>通过调试日志验证</t>
+  </si>
+  <si>
+    <t>URS-SW-002</t>
+  </si>
+  <si>
+    <t>上电后执行内置自检（BIT），包括：存储器测试、通信环路测试、探测器通信测试</t>
+  </si>
+  <si>
+    <t>自检结果可通过状态码上报；故障时输出错误码并进入安全模式</t>
+  </si>
+  <si>
+    <t>模拟各故障，验证自检覆盖率≥95%</t>
+  </si>
+  <si>
+    <t>URS-SW-003</t>
+  </si>
+  <si>
+    <t>模式切换时间≤0.5秒（同URS-FUN-003）</t>
+  </si>
+  <si>
+    <t>通过指令触发模式切换，测量响应时间</t>
+  </si>
+  <si>
+    <t>URS-SW-004</t>
+  </si>
+  <si>
+    <t>在初始捕获模式下，软件自动搜索全天球识别恒星，若无先验姿态则采用全星图识别算法</t>
+  </si>
+  <si>
+    <t>捕获时间≤30秒（冷启动时间）</t>
+  </si>
+  <si>
+    <t>模拟不同星图，统计捕获成功率≥95%</t>
+  </si>
+  <si>
+    <t>URS-SW-005</t>
+  </si>
+  <si>
+    <t>在跟踪模式下，软件利用上一帧姿态预测当前星点位置，仅对预测区域进行星点提取和匹配</t>
+  </si>
+  <si>
+    <t>跟踪帧率≥5Hz（与URS-PER-004一致）</t>
+  </si>
+  <si>
+    <t>连续跟踪1000帧，丢帧率≤1%</t>
+  </si>
+  <si>
+    <t>URS-SW-006</t>
+  </si>
+  <si>
+    <t>软件支持配置曝光时间、增益、图像窗口等参数（与URS-OP-002对应）</t>
+  </si>
+  <si>
+    <t>参数修改后下一帧生效</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>通过指令修改，验证图像亮度变化</t>
+  </si>
+  <si>
+    <t>URS-SW-007</t>
+  </si>
+  <si>
+    <t>软件实时提取星点质心，亚像素质心定位精度≤0.05像素（RMS）</t>
+  </si>
+  <si>
+    <t>在仿真星点下测试</t>
+  </si>
+  <si>
+    <t>使用高斯星点模拟，计算质心误差</t>
+  </si>
+  <si>
+    <t>URS-SW-008</t>
+  </si>
+  <si>
+    <t>支持星图存储功能，可存储最近100帧原始图像（与URS-FUN-005对应）</t>
+  </si>
+  <si>
+    <t>存储的图像可回放并正确解析</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>触发存储指令，检查存储介质</t>
+  </si>
+  <si>
+    <t>URS-SW-009</t>
+  </si>
+  <si>
+    <t>软件内置高精度星表（至少包含6等星），支持三角形算法或栅格算法进行星识别</t>
+  </si>
+  <si>
+    <t>识别成功率≥95%（与URS-FUN-001一致）</t>
+  </si>
+  <si>
+    <t>在不同视场星数下测试</t>
+  </si>
+  <si>
+    <t>URS-SW-010</t>
+  </si>
+  <si>
+    <t>输出格式经标准工具校验通过</t>
+  </si>
+  <si>
+    <t>抓取数据包解析验证</t>
+  </si>
+  <si>
+    <t>URS-SW-011</t>
+  </si>
+  <si>
+    <t>在跟踪模式下，姿态更新率可在0.5~5Hz范围内配置（与URS-PER-004一致）</t>
+  </si>
+  <si>
+    <t>配置后实际输出频率误差≤1%</t>
+  </si>
+  <si>
+    <t>测量输出脉冲间隔</t>
+  </si>
+  <si>
+    <t>URS-SW-012</t>
+  </si>
+  <si>
+    <t>姿态输出延迟（从曝光开始到数据输出）≤100ms（与URS-PER-005一致）</t>
+  </si>
+  <si>
+    <t>用示波器测量同步信号与数据输出时间差</t>
+  </si>
+  <si>
+    <t>连续测量100次，最大值≤100ms</t>
+  </si>
+  <si>
+    <t>通信与遥测</t>
+  </si>
+  <si>
+    <t>URS-SW-013</t>
+  </si>
+  <si>
+    <t>实现RS422/UART通信协议，帧格式包含帧头、长度、数据、CRC校验（与URS-COM-001一致）</t>
+  </si>
+  <si>
+    <t>误码率≤10⁻⁶，CRC能检测所有单比特错误</t>
+  </si>
+  <si>
+    <t>通过串口调试助手模拟干扰</t>
+  </si>
+  <si>
+    <t>URS-SW-014</t>
+  </si>
+  <si>
+    <t>周期性输出遥测参数：温度、电压、当前星数、工作模式、错误码（与URS-COM-002一致）</t>
+  </si>
+  <si>
+    <t>输出频率≥1Hz，数据正确</t>
+  </si>
+  <si>
+    <t>对比实际传感器读数</t>
+  </si>
+  <si>
+    <t>URS-SW-015</t>
+  </si>
+  <si>
+    <t>支持遥控指令：重置、模式切换、参数设置、固件升级（与URS-COM-003一致）</t>
+  </si>
+  <si>
+    <t>指令响应时间≤100ms</t>
+  </si>
+  <si>
+    <t>发送指令验证功能</t>
+  </si>
+  <si>
+    <t>参数管理与存储</t>
+  </si>
+  <si>
+    <t>URS-SW-016</t>
+  </si>
+  <si>
+    <t>关键参数（如曝光时间、增益、输出频率、校准参数）存储在非易失存储器中，掉电不丢失</t>
+  </si>
+  <si>
+    <t>断电重启后参数恢复</t>
+  </si>
+  <si>
+    <t>修改参数后断电重启，读取验证</t>
+  </si>
+  <si>
+    <t>URS-SW-017</t>
+  </si>
+  <si>
+    <t>参数修改需通过特定指令，并具有合理性检查（如曝光时间范围1~500ms）</t>
+  </si>
+  <si>
+    <t>超范围参数拒绝并返回错误码</t>
+  </si>
+  <si>
+    <t>尝试写入非法值</t>
+  </si>
+  <si>
+    <t>固件升级</t>
+  </si>
+  <si>
+    <t>URS-SW-018</t>
+  </si>
+  <si>
+    <t>支持通过UART或USB接口进行固件升级，升级过程中断点续传或校验失败后自动回滚</t>
+  </si>
+  <si>
+    <t>升级成功率≥99%，升级后版本号正确</t>
+  </si>
+  <si>
+    <t>模拟升级中断，验证回滚机制</t>
+  </si>
+  <si>
+    <t>故障诊断与处理</t>
+  </si>
+  <si>
+    <t>URS-SW-019</t>
+  </si>
+  <si>
+    <t>软件实时监测探测器温度、电源电压、通信状态，发现异常时记录错误码并上报（与URS-SAF-007对应）</t>
+  </si>
+  <si>
+    <t>触发阈值时1秒内上报</t>
+  </si>
+  <si>
+    <t>模拟过温、通信断开</t>
+  </si>
+  <si>
+    <t>URS-SW-020</t>
+  </si>
+  <si>
+    <t>当连续多帧无法识别星点时，自动切换至初始捕获模式</t>
+  </si>
+  <si>
+    <t>连续5帧无识别则切换</t>
+  </si>
+  <si>
+    <t>遮挡镜头，验证模式切换</t>
+  </si>
+  <si>
+    <t>安全与可靠性</t>
+  </si>
+  <si>
+    <t>URS-SW-021</t>
+  </si>
+  <si>
+    <t>软件配合硬件看门狗，周期喂狗，超时（1.6秒）未喂狗则硬件复位（与URS-SAF-005对应）</t>
+  </si>
+  <si>
+    <t>软件死锁后系统自动重启</t>
+  </si>
+  <si>
+    <t>注入死循环，观察复位</t>
+  </si>
+  <si>
+    <t>URS-SW-022</t>
+  </si>
+  <si>
+    <t>关键数据（如星表、校准参数）采用三重冗余存储，并具有EDAC纠错能力（与URS-SAF-006对应）</t>
+  </si>
+  <si>
+    <t>单比特错误可自动纠正，双比特错误可检测</t>
+  </si>
+  <si>
+    <t>注入存储器错误，验证恢复</t>
+  </si>
+  <si>
+    <t>URS-SW-023</t>
+  </si>
+  <si>
+    <t>软件模块化设计，各任务独立（如采集、识别、通信），使用看门狗监控各任务运行状态</t>
+  </si>
+  <si>
+    <t>单个任务崩溃不影响其他任务</t>
+  </si>
+  <si>
+    <t>模拟任务挂起，检查系统响应</t>
+  </si>
+  <si>
+    <t>实时性与资源</t>
+  </si>
+  <si>
+    <t>URS-SW-024</t>
+  </si>
+  <si>
+    <t>软件任务调度满足实时性要求，图像处理周期≤200ms（对应5Hz更新率）</t>
+  </si>
+  <si>
+    <t>最大处理时间≤180ms（留有余量）</t>
+  </si>
+  <si>
+    <t>统计1000次处理时间</t>
+  </si>
+  <si>
+    <t>URS-SW-025</t>
+  </si>
+  <si>
+    <t>软件代码遵循MISRA C或类似安全编码规范，静态分析无高风险缺陷</t>
+  </si>
+  <si>
+    <t>通过静态分析工具检查</t>
+  </si>
+  <si>
+    <t>提供分析报告</t>
+  </si>
+  <si>
+    <t>文档与交付</t>
+  </si>
+  <si>
+    <t>URS-SW-026</t>
+  </si>
+  <si>
+    <t>交付软件源代码及注释，符合编码规范（与URS-DOC-006对应）</t>
+  </si>
+  <si>
+    <t>代码通过评审</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>URS-SW-027</t>
+  </si>
+  <si>
+    <t>提供软件设计说明文档，包含架构、模块接口、数据结构、算法说明</t>
+  </si>
+  <si>
+    <t>文档通过评审</t>
+  </si>
+  <si>
+    <t>软件支持三种工作模式：初始捕获模式、跟踪模式、待机模式</t>
+  </si>
+  <si>
+    <t>功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作模式管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星图采集与处理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿态解算输出四元数，符合CCSDS 500.0-B-4标准（与URS-FUN-002一致）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星识别与姿态解算</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -916,7 +1294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -933,14 +1311,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -967,18 +1343,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1260,17 +1643,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.9140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1284,7 +1667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1298,7 +1681,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1312,7 +1695,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1326,7 +1709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1340,7 +1723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1361,70 +1744,70 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C39249B0-3355-4D46-AAA9-E7FA14858D6A}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE280B0B-1317-48D2-B109-1FAD148DFDF0}">
+  <dimension ref="A13:D16"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" t="s">
         <v>131</v>
       </c>
-      <c r="B1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="C16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" t="s">
         <v>137</v>
-      </c>
-      <c r="B2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="42" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -1434,54 +1817,70 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4473B0-A9DE-4D23-92D4-88837E1CED78}">
-  <dimension ref="A22:D24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C39249B0-3355-4D46-AAA9-E7FA14858D6A}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" t="s">
         <v>147</v>
       </c>
-      <c r="D22" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>159</v>
-      </c>
-      <c r="B23" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D23" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>160</v>
-      </c>
-      <c r="B24" t="s">
-        <v>162</v>
-      </c>
-      <c r="C24" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" t="s">
-        <v>164</v>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1491,67 +1890,54 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADCFBB3E-29CF-4454-AA4A-DDE163285BAF}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4473B0-A9DE-4D23-92D4-88837E1CED78}">
+  <dimension ref="A22:D24"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" t="s">
-        <v>177</v>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1561,46 +1947,67 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1EA3AA-6D10-457B-ABDA-BCED1C2FE1FB}">
-  <dimension ref="A2:C4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADCFBB3E-29CF-4454-AA4A-DDE163285BAF}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>158</v>
+      </c>
+      <c r="B2" t="s">
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>184</v>
+        <v>159</v>
+      </c>
+      <c r="B3" t="s">
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -1610,10 +2017,49 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7976B69F-B5DF-4D4C-A17E-223D0B2BE655}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F1EA3AA-6D10-457B-ABDA-BCED1C2FE1FB}">
+  <dimension ref="A2:C4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1621,98 +2067,87 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CE70FB6-91F3-4A8F-A331-D25AF351077F}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.9296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" t="s">
         <v>189</v>
       </c>
-      <c r="B2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" t="s">
         <v>190</v>
       </c>
-      <c r="B3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C6" t="s">
         <v>191</v>
       </c>
-      <c r="B4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" t="s">
         <v>192</v>
-      </c>
-      <c r="B5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B6" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -1724,102 +2159,102 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F305BAA-1386-4B9B-81B6-012C2654E93B}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="C1" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="D1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" t="s">
         <v>210</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" t="s">
         <v>211</v>
       </c>
-      <c r="C2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C6" t="s">
         <v>212</v>
       </c>
-      <c r="C3" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" t="s">
         <v>213</v>
       </c>
-      <c r="C4" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" t="s">
         <v>214</v>
-      </c>
-      <c r="C5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -1831,14 +2266,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E31F7DD-AF41-4FC1-8EF9-65504671B989}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.9140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1852,7 +2287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1863,10 +2298,10 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1877,24 +2312,24 @@
         <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="56" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:4">
       <c r="C9" s="1"/>
     </row>
   </sheetData>
@@ -1905,16 +2340,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1D26352-68E4-4427-A6EF-8EBED87B4B98}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
     <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1922,86 +2358,96 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
+        <v>219</v>
+      </c>
+      <c r="E1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="28" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="E4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
         <v>47</v>
       </c>
-      <c r="C4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="364" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2010,118 +2456,599 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A7084B-7203-4AFD-BB54-7DA6D919CD3B}">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BAD7A82-868F-4154-8BB7-46AFF9ADA3A4}">
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="1" max="2" width="16.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="83.3984375" customWidth="1"/>
+    <col min="4" max="4" width="57.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>31</v>
-      </c>
       <c r="D1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>55</v>
+        <v>236</v>
+      </c>
+      <c r="E1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="6" t="s">
+        <v>239</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>241</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="E2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="6"/>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>246</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>58</v>
+        <v>247</v>
+      </c>
+      <c r="E3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>249</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>355</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="E5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="6"/>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>254</v>
+      </c>
+      <c r="E6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="7"/>
+      <c r="B7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F9" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6"/>
+      <c r="B10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E10" t="s">
+        <v>243</v>
+      </c>
+      <c r="F10" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6"/>
+      <c r="B11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" t="s">
+        <v>271</v>
+      </c>
+      <c r="E11" t="s">
+        <v>272</v>
+      </c>
+      <c r="F11" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C13" t="s">
+        <v>275</v>
+      </c>
+      <c r="D13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F13" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6"/>
+      <c r="B14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" t="s">
+        <v>359</v>
+      </c>
+      <c r="D14" t="s">
+        <v>279</v>
+      </c>
+      <c r="E14" t="s">
+        <v>243</v>
+      </c>
+      <c r="F14" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6"/>
+      <c r="B15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C15" t="s">
+        <v>282</v>
+      </c>
+      <c r="D15" t="s">
+        <v>283</v>
+      </c>
+      <c r="E15" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6"/>
+      <c r="B16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D16" t="s">
+        <v>287</v>
+      </c>
+      <c r="E16" t="s">
+        <v>243</v>
+      </c>
+      <c r="F16" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" t="s">
+        <v>291</v>
+      </c>
+      <c r="D18" t="s">
+        <v>292</v>
+      </c>
+      <c r="E18" t="s">
+        <v>243</v>
+      </c>
+      <c r="F18" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="6"/>
+      <c r="B19" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" t="s">
+        <v>295</v>
+      </c>
+      <c r="D19" t="s">
+        <v>296</v>
+      </c>
+      <c r="E19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="6"/>
+      <c r="B20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C20" t="s">
+        <v>299</v>
+      </c>
+      <c r="D20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" t="s">
+        <v>243</v>
+      </c>
+      <c r="F20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="7"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B22" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" t="s">
+        <v>305</v>
+      </c>
+      <c r="E22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F22" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="6"/>
+      <c r="B23" t="s">
+        <v>307</v>
+      </c>
+      <c r="C23" t="s">
+        <v>308</v>
+      </c>
+      <c r="D23" t="s">
+        <v>309</v>
+      </c>
+      <c r="E23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F23" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B25" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25" t="s">
+        <v>313</v>
+      </c>
+      <c r="D25" t="s">
+        <v>314</v>
+      </c>
+      <c r="E25" t="s">
+        <v>263</v>
+      </c>
+      <c r="F25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="7"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" t="s">
+        <v>317</v>
+      </c>
+      <c r="C27" t="s">
+        <v>318</v>
+      </c>
+      <c r="D27" t="s">
+        <v>319</v>
+      </c>
+      <c r="E27" t="s">
+        <v>243</v>
+      </c>
+      <c r="F27" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="6"/>
+      <c r="B28" t="s">
+        <v>321</v>
+      </c>
+      <c r="C28" t="s">
+        <v>322</v>
+      </c>
+      <c r="D28" t="s">
+        <v>323</v>
+      </c>
+      <c r="E28" t="s">
+        <v>263</v>
+      </c>
+      <c r="F28" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="7"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B30" t="s">
+        <v>326</v>
+      </c>
+      <c r="C30" t="s">
+        <v>327</v>
+      </c>
+      <c r="D30" t="s">
+        <v>328</v>
+      </c>
+      <c r="E30" t="s">
+        <v>243</v>
+      </c>
+      <c r="F30" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="6"/>
+      <c r="B31" t="s">
+        <v>330</v>
+      </c>
+      <c r="C31" t="s">
+        <v>331</v>
+      </c>
+      <c r="D31" t="s">
+        <v>332</v>
+      </c>
+      <c r="E31" t="s">
+        <v>243</v>
+      </c>
+      <c r="F31" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="6"/>
+      <c r="B32" t="s">
+        <v>334</v>
+      </c>
+      <c r="C32" t="s">
+        <v>335</v>
+      </c>
+      <c r="D32" t="s">
+        <v>336</v>
+      </c>
+      <c r="E32" t="s">
+        <v>243</v>
+      </c>
+      <c r="F32" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B34" t="s">
+        <v>339</v>
+      </c>
+      <c r="C34" t="s">
+        <v>340</v>
+      </c>
+      <c r="D34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E34" t="s">
+        <v>243</v>
+      </c>
+      <c r="F34" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="6"/>
+      <c r="B35" t="s">
+        <v>343</v>
+      </c>
+      <c r="C35" t="s">
+        <v>344</v>
+      </c>
+      <c r="D35" t="s">
+        <v>345</v>
+      </c>
+      <c r="E35" t="s">
+        <v>243</v>
+      </c>
+      <c r="F35" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B37" t="s">
+        <v>348</v>
+      </c>
+      <c r="C37" t="s">
+        <v>349</v>
+      </c>
+      <c r="D37" t="s">
+        <v>350</v>
+      </c>
+      <c r="E37" t="s">
+        <v>263</v>
+      </c>
+      <c r="F37" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="6"/>
+      <c r="B38" t="s">
+        <v>352</v>
+      </c>
+      <c r="C38" t="s">
+        <v>353</v>
+      </c>
+      <c r="D38" t="s">
+        <v>354</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A22:A23"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A1FC3D3-6BFA-4788-9AA1-C4679BD1709C}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A7084B-7203-4AFD-BB54-7DA6D919CD3B}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.9140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="55.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2129,52 +3056,83 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="42" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>82</v>
+        <v>60</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2184,84 +3142,70 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FA63635-8948-4287-BF8F-79482F725BED}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A1FC3D3-6BFA-4788-9AA1-C4679BD1709C}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="28" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2271,84 +3215,84 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF54E86F-CCF1-4ECE-A9ED-6A3FB6CAF1B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FA63635-8948-4287-BF8F-79482F725BED}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2358,60 +3302,84 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06995820-E9F1-4CC3-88D7-29F65554791B}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF54E86F-CCF1-4ECE-A9ED-6A3FB6CAF1B3}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.58203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="D2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>105</v>
+      </c>
+      <c r="D4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2421,70 +3389,60 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE280B0B-1317-48D2-B109-1FAD148DFDF0}">
-  <dimension ref="A13:D16"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06995820-E9F1-4CC3-88D7-29F65554791B}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.4140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" t="s">
         <v>119</v>
       </c>
-      <c r="D13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>134</v>
-      </c>
-      <c r="B14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" t="s">
-        <v>145</v>
-      </c>
-      <c r="D16" t="s">
-        <v>146</v>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
